--- a/education_forms/037_sacraments_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/037_sacraments_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,24 +538,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sacraments_important_points</t>
+          <t>sacrament_of_baptism</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are the important points</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>What are the key points of the Sacraments that every student must know?</t>
-        </is>
-      </c>
+          <t>What is the Sacrament of Baptism?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -570,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>sacrament_of_confirmation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the Sacrament of Penance</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>What is the purpose and significance of the sacrament of Penance?</t>
-        </is>
-      </c>
+          <t>What is the purpose and significance of the Sacrament of Confirmation?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -597,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>eucharist_sacrament</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Sacrament of Reconciliation?</t>
+          <t>What is the Sacrament of the Eucharist?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -620,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>sacrament_of_penance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Sacrament of the Eucharist?</t>
+          <t>What is the purpose and significance of the Sacrament of Penance?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -643,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>anointing_of_the_sick</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Sacrament of Baptism?</t>
+          <t>What is the purpose and significance of the Sacrament of Anointing of the Sick?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -666,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>holy_orders</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Sacrament of Confirmation?</t>
+          <t>What is the purpose and significance of the Sacrament of Holy Orders?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -689,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>matrimony</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Anointing of the Sick?</t>
+          <t>What is the Sacrament of Matrimony?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -712,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sacraments_description</t>
+          <t>reconciliation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the purpose and significance of the Sacrament of Holy Orders?</t>
+          <t>What is the Sacrament of Reconciliation?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>Can you describe the Sacrament of Baptism?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>final_description</t>
+          <t>final_question_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Final Description</t>
+          <t>Can you describe the Sacrament of Confirmation?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>Can you describe the Sacrament of the Eucharist?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -804,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>final_description</t>
+          <t>final_question_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Final Description</t>
+          <t>Can you describe the Sacrament of Penance?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>Can you describe the Sacrament of Anointing of the Sick?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -850,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>final_description</t>
+          <t>final_question_6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Final Description</t>
+          <t>Can you explain the Sacrament of Holy Orders?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -868,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>Can you describe the Sacrament of Matrimony?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -891,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>final_description</t>
+          <t>final_question_8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Final Description</t>
+          <t>Which of the following is a sacrament that is considered a sacrament of healing?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -919,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>What is the purpose and significance of the Sacrament of the Anointing of the Sick?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -942,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>final_description</t>
+          <t>final_question_10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Final Description</t>
+          <t>Final Question 10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -960,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>final_question</t>
+          <t>final_question_11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Final Question</t>
+          <t>Can you explain the Sacrament of Matrimony?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>final_description</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Final Description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>final_question</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Final Question</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>final_description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Final Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>final_question</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Final Question</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>final_description</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Final Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,391 +1011,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sacraments_important_points_choices</t>
+          <t>final_question_8_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sacrament_of_baptism</t>
+          <t>sacrament_of_penance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacrament of Baptism</t>
+          <t>Sacrament of Penance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sacraments_important_points_choices</t>
+          <t>final_question_8_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sacrament_of_the_eucharist</t>
+          <t>sacrament_of_anointing_of_the_sick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sacrament of the Eucharist</t>
+          <t>Sacrament of Anointing of the Sick</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sacraments_important_points_choices</t>
+          <t>final_question_8_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sacrament_of_the_sick</t>
+          <t>sacrament_of_the_eucharist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sacrament of the Sick</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sacrament_of_holy_orders</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sacrament of Holy Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sacrament_of_matrimony</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sacrament of Matrimony</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sacrament_of_the_anointing_of_the_sick</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sacrament of the Anointing of the Sick</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>sacrament_of_holy_orders</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sacrament of Holy Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>confirmation</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>anointing_of_the_sick</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Anointing of the Sick</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>holy_orders</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Holy Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sacraments_important_points_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>penance</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Penance</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>final_question_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 5</t>
+          <t>Sacrament of the Eucharist</t>
         </is>
       </c>
     </row>
